--- a/dataset/construct/dataset_splits/data_size/50_percent/tum/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/50_percent/tum/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1698</v>
+        <v>954</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,83 +625,85 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>87.9844727735949</v>
+        <v>78.7770593771389</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>28.2283864654296</v>
       </c>
       <c r="E2" t="n">
-        <v>30.1160023795359</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>488</v>
+      </c>
+      <c r="I2" t="n">
+        <v>578</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>386</v>
       </c>
       <c r="K2" t="n">
-        <v>282</v>
+        <v>1452</v>
       </c>
       <c r="L2" t="n">
-        <v>487</v>
+        <v>111</v>
       </c>
       <c r="M2" t="n">
-        <v>571</v>
+        <v>54</v>
       </c>
       <c r="N2" t="n">
-        <v>1340</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="P2" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="Q2" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>234</v>
+        <v>36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X2" t="n">
-        <v>27.35</v>
+        <v>22.8163986665956</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.218241042345277</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>28.3295136236313</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>27.6120628833503</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -725,36 +712,27 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>136</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>284</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2106</v>
+        <v>1314</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,77 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>87.3656652597156</v>
+        <v>79.1469129464852</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>31.833910034602</v>
       </c>
       <c r="E3" t="n">
-        <v>29.0858725761772</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>45</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>120.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>175.9</v>
+      </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>229.1</v>
       </c>
       <c r="K3" t="n">
-        <v>327.7</v>
+        <v>525.5</v>
       </c>
       <c r="L3" t="n">
-        <v>332.3</v>
+        <v>35.9</v>
       </c>
       <c r="M3" t="n">
-        <v>320.1</v>
+        <v>28.7</v>
       </c>
       <c r="N3" t="n">
-        <v>980.1</v>
+        <v>27.5</v>
       </c>
       <c r="O3" t="n">
-        <v>19.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>58.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>24.2869875222816</v>
       </c>
       <c r="X3" t="n">
-        <v>27.45</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.26813880126183</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.0244461420932</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.4032150535234</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -859,22 +839,13 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2246</v>
+        <v>474</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -882,77 +853,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>76.92898734377771</v>
+        <v>78.2075977577509</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>27.6816608996539</v>
       </c>
       <c r="E4" t="n">
-        <v>22.7244034844085</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>49</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="I4" t="n">
+        <v>222</v>
+      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K4" t="n">
-        <v>225.3</v>
+        <v>630</v>
       </c>
       <c r="L4" t="n">
-        <v>178.6</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
-        <v>267.7</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
-        <v>671.6</v>
+        <v>23</v>
       </c>
       <c r="O4" t="n">
-        <v>25.6</v>
+        <v>59</v>
       </c>
       <c r="P4" t="n">
-        <v>90.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>211.9</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>54.7</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>63.1</v>
+        <v>26.8</v>
       </c>
       <c r="V4" t="n">
-        <v>117.8</v>
+        <v>0.21</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>26.7379679144385</v>
       </c>
       <c r="X4" t="n">
-        <v>24.5</v>
+        <v>26.4345313179585</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.298611111111111</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.6052966641202</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.9831715115263</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -964,39 +937,28 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>168</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>340</v>
+        <v>656</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1004,41 +966,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>79.8069135485588</v>
+        <v>86.7305080868</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>21.3406795224977</v>
       </c>
       <c r="E5" t="n">
-        <v>27.6816608996539</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>286.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>357.2</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>166.4</v>
       </c>
       <c r="K5" t="n">
-        <v>520</v>
+        <v>810.4</v>
       </c>
       <c r="L5" t="n">
-        <v>304</v>
+        <v>12.2</v>
       </c>
       <c r="M5" t="n">
-        <v>172</v>
+        <v>28.3</v>
       </c>
       <c r="N5" t="n">
-        <v>996</v>
+        <v>5.7</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>46.2</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1047,37 +1011,37 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>23.7458619811561</v>
       </c>
       <c r="X5" t="n">
-        <v>25.75</v>
+        <v>23.5115010765807</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.217993079584775</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>25.528393175452</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>25.055148236001</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1089,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1101,24 +1065,13 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>91</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>180</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>914</v>
+        <v>1427</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1126,79 +1079,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84.0671732958146</v>
+        <v>86.99098473901689</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>25.2080856123662</v>
       </c>
       <c r="E6" t="n">
-        <v>25.7629805786761</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>319.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1400</v>
+        <v>203</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>264.3</v>
       </c>
       <c r="K6" t="n">
-        <v>855</v>
+        <v>786.8</v>
       </c>
       <c r="L6" t="n">
-        <v>534</v>
+        <v>36.6</v>
       </c>
       <c r="M6" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1817</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>50</v>
+        <v>36.6</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>93</v>
+        <v>22.35</v>
       </c>
       <c r="V6" t="n">
-        <v>93</v>
+        <v>0.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>23.0137509549274</v>
       </c>
       <c r="X6" t="n">
-        <v>29</v>
+        <v>22.1512191514658</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.220858895705522</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>29.921059332824</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>29.2679951700071</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1219,28 +1172,21 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
         <v>154</v>
       </c>
-      <c r="AN6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>922</v>
+        <v>515</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1248,91 +1194,91 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75.0324815258448</v>
+        <v>78.3007491063959</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>23.2356317012401</v>
       </c>
       <c r="E7" t="n">
-        <v>26.4721074380165</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>629</v>
       </c>
       <c r="I7" t="n">
-        <v>1120</v>
+        <v>562</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>620</v>
       </c>
       <c r="K7" t="n">
-        <v>280</v>
+        <v>1811</v>
       </c>
       <c r="L7" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>306</v>
+        <v>27</v>
       </c>
       <c r="N7" t="n">
-        <v>977</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="P7" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>27.75</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>27.947542653425</v>
       </c>
       <c r="X7" t="n">
-        <v>26.5</v>
+        <v>26.973142863685</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.22742474916388</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>27.3745861981156</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>26.7218716216114</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1347,22 +1293,15 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>242</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1265</v>
+        <v>2601</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1370,85 +1309,85 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>52.5566858379598</v>
+        <v>80.6226186402008</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>34.2403214024835</v>
       </c>
       <c r="E8" t="n">
-        <v>20.0065693212696</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>46</v>
+        <v>377</v>
       </c>
       <c r="I8" t="n">
-        <v>4500</v>
+        <v>83</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="K8" t="n">
-        <v>328</v>
+        <v>543</v>
       </c>
       <c r="L8" t="n">
-        <v>242</v>
+        <v>59</v>
       </c>
       <c r="M8" t="n">
-        <v>345</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>915</v>
+        <v>15</v>
       </c>
       <c r="O8" t="n">
-        <v>183</v>
+        <v>86</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="Q8" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>199</v>
+        <v>53</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>136</v>
+        <v>23.15</v>
       </c>
       <c r="V8" t="n">
-        <v>335</v>
+        <v>0.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>23.1410746116628</v>
       </c>
       <c r="X8" t="n">
-        <v>25.45</v>
+        <v>22.7940734179357</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.162454873646209</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>25.4647313470843</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>25.2524956816771</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1468,25 +1407,12 @@
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>118</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>132</v>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>645</v>
+        <v>688</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1494,85 +1420,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85.26030306487181</v>
+        <v>86.5826564757776</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>28.7639710716633</v>
       </c>
       <c r="E9" t="n">
-        <v>23.2334561768947</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="I9" t="n">
-        <v>196</v>
+        <v>240.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>281.9</v>
       </c>
       <c r="K9" t="n">
-        <v>114</v>
+        <v>1002.1</v>
       </c>
       <c r="L9" t="n">
-        <v>145</v>
+        <v>46.7</v>
       </c>
       <c r="M9" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>389</v>
+        <v>37.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>104.8</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>42</v>
+        <v>22.25</v>
       </c>
       <c r="V9" t="n">
-        <v>42</v>
+        <v>0.18</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>22.2498090145149</v>
       </c>
       <c r="X9" t="n">
-        <v>21.4</v>
+        <v>22.0244421422418</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.238683127572017</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.6450216450216</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.2868030290747</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1581,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1593,19 +1519,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>72</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>238</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -1621,37 +1538,37 @@
         <v>87.1663702246052</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>32.3883554336229</v>
       </c>
       <c r="E10" t="n">
-        <v>32.3883554336229</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>75.7</v>
       </c>
       <c r="I10" t="n">
-        <v>2430</v>
+        <v>61.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>26.8</v>
       </c>
       <c r="K10" t="n">
-        <v>75.7</v>
+        <v>164.1</v>
       </c>
       <c r="L10" t="n">
-        <v>61.6</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>164.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
@@ -1663,34 +1580,34 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>22.895</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>22.7591036414566</v>
       </c>
       <c r="X10" t="n">
-        <v>22.895</v>
+        <v>22.1942730679895</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.238168526356291</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.7591036414566</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>22.1942730679895</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1705,36 +1622,27 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN10" t="n">
         <v>160</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>576</v>
+        <v>550</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1742,88 +1650,88 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.5730949121606</v>
+        <v>82.4873716632443</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>24.4897959183673</v>
       </c>
       <c r="E11" t="n">
-        <v>26.2975778546712</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
+        <v>694</v>
       </c>
       <c r="I11" t="n">
-        <v>745</v>
+        <v>856</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1059</v>
       </c>
       <c r="K11" t="n">
-        <v>483.4</v>
+        <v>2609</v>
       </c>
       <c r="L11" t="n">
-        <v>564.9</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>380.1</v>
+        <v>117</v>
       </c>
       <c r="N11" t="n">
-        <v>1428.4</v>
+        <v>48</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="P11" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.1</v>
+        <v>11</v>
       </c>
       <c r="R11" t="n">
-        <v>32.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>26.4196587726</v>
       </c>
       <c r="X11" t="n">
-        <v>26.35</v>
+        <v>25.6028939368547</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.201365187713311</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>26.5469824293354</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>26.0806653934161</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1835,30 +1743,19 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>166</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1705</v>
+        <v>2257</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1866,91 +1763,91 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>85.11794274596291</v>
+        <v>68.1240494207418</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>24.4897959183673</v>
       </c>
       <c r="E12" t="n">
-        <v>23.0400201994697</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>38.4</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>338.1</v>
       </c>
       <c r="I12" t="n">
-        <v>25500</v>
+        <v>245.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>290.6</v>
       </c>
       <c r="K12" t="n">
-        <v>1413.6</v>
+        <v>874.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1288</v>
+        <v>61.6</v>
       </c>
       <c r="M12" t="n">
-        <v>1236</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3937.6</v>
+        <v>13.8</v>
       </c>
       <c r="O12" t="n">
-        <v>379</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>997</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>650</v>
+        <v>27.65</v>
       </c>
       <c r="V12" t="n">
-        <v>851.5</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>27.2154316271963</v>
       </c>
       <c r="X12" t="n">
-        <v>30.15</v>
+        <v>26.9211850934372</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.161585365853658</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>29.8892284186402</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>29.6417868004739</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -1965,24 +1862,15 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>232</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2636</v>
+        <v>704</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1990,83 +1878,85 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>85.0193633229396</v>
+        <v>85.76208647045399</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>24.609375</v>
       </c>
       <c r="E13" t="n">
-        <v>27.1314117909923</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>51</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>514.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>174.8</v>
+      </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>420.7</v>
       </c>
       <c r="K13" t="n">
-        <v>560</v>
+        <v>1109.9</v>
       </c>
       <c r="L13" t="n">
-        <v>472</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>603</v>
+        <v>13.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1635</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>87.3</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>69</v>
+        <v>5.7</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>22.85</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>23.7140310669722</v>
       </c>
       <c r="X13" t="n">
-        <v>28.4</v>
+        <v>22.9332496617824</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.230529595015576</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>27.8838808250573</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>27.2524701589629</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2075,36 +1965,25 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>124</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>210</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>471</v>
+        <v>556</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2112,79 +1991,79 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75.0402101553984</v>
+        <v>78.32835766978479</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>25.8264462809917</v>
       </c>
       <c r="E14" t="n">
-        <v>24.2105958514995</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>55</v>
+        <v>855</v>
       </c>
       <c r="I14" t="n">
-        <v>200</v>
+        <v>523</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>457</v>
       </c>
       <c r="K14" t="n">
-        <v>464</v>
+        <v>1835</v>
       </c>
       <c r="L14" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1824</v>
+        <v>77</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>24.95</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>26.1013496307614</v>
       </c>
       <c r="X14" t="n">
-        <v>25.8</v>
+        <v>24.9992044677091</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.6557168321874</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.7175864208069</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2193,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2202,33 +2081,24 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2236,79 +2106,79 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79.1056030876873</v>
+        <v>77.5943455776105</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>34.2058298631766</v>
       </c>
       <c r="E15" t="n">
-        <v>25.390625</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>376.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5640</v>
+        <v>275.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>276.5</v>
       </c>
       <c r="K15" t="n">
-        <v>282</v>
+        <v>928.5</v>
       </c>
       <c r="L15" t="n">
-        <v>283</v>
+        <v>25.6</v>
       </c>
       <c r="M15" t="n">
-        <v>266</v>
+        <v>33.7</v>
       </c>
       <c r="N15" t="n">
-        <v>831</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>158</v>
+        <v>123.9</v>
       </c>
       <c r="P15" t="n">
-        <v>41</v>
+        <v>22.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>22.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>24.55</v>
       </c>
       <c r="V15" t="n">
-        <v>17</v>
+        <v>0.19</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>24.859943977591</v>
       </c>
       <c r="X15" t="n">
-        <v>24.4</v>
+        <v>24.5496573149696</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.281690140845071</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>24.5098039215686</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.8260951566085</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2317,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2335,24 +2205,13 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>146</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2419</v>
+        <v>2302</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2360,85 +2219,85 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>83.00703576951349</v>
+        <v>91.7489835728953</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>21.2244897959183</v>
       </c>
       <c r="E16" t="n">
-        <v>24.1588179685585</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>40</v>
+        <v>216.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1960</v>
+        <v>32.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>441.3</v>
+        <v>340</v>
       </c>
       <c r="L16" t="n">
-        <v>341.5</v>
+        <v>22.2</v>
       </c>
       <c r="M16" t="n">
-        <v>36.7</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>819.5</v>
+        <v>6.1</v>
       </c>
       <c r="O16" t="n">
-        <v>36.3</v>
+        <v>28.3</v>
       </c>
       <c r="P16" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>63.8</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>21.8678380443086</v>
       </c>
       <c r="X16" t="n">
-        <v>22.95</v>
+        <v>21.3763064498772</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.171314741035857</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>23.4275528393175</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>23.0743446333452</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2450,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2459,24 +2318,15 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>234</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2338</v>
+        <v>1720</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2484,121 +2334,114 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>89.2657497718458</v>
+        <v>68.3052995474941</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>30.7173999207292</v>
       </c>
       <c r="E17" t="n">
-        <v>25.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>166.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>262</v>
+      </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="K17" t="n">
-        <v>237.9</v>
+        <v>676.7</v>
       </c>
       <c r="L17" t="n">
-        <v>111.4</v>
+        <v>44.4</v>
       </c>
       <c r="M17" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>391.7</v>
+        <v>95.2</v>
       </c>
       <c r="O17" t="n">
-        <v>72.8</v>
+        <v>139.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>102.5</v>
+        <v>99.8</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>123.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>46.5</v>
+        <v>24.25</v>
       </c>
       <c r="V17" t="n">
-        <v>46.5</v>
+        <v>0.29</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X17" t="n">
-        <v>19.65</v>
+        <v>23.0936433298824</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.205479452054795</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.9261522790935</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.6934438757455</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>220</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>977</v>
+        <v>643</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2606,91 +2449,91 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>75.4642704134662</v>
+        <v>77.2277739752072</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>33.802055164954</v>
       </c>
       <c r="E18" t="n">
-        <v>23.7196092506476</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
+        <v>289</v>
+      </c>
+      <c r="I18" t="n">
+        <v>594</v>
+      </c>
+      <c r="J18" t="n">
+        <v>377</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L18" t="n">
         <v>35</v>
       </c>
-      <c r="I18" t="n">
-        <v>2740</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>663.9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>413.8</v>
-      </c>
       <c r="M18" t="n">
-        <v>672</v>
+        <v>23</v>
       </c>
       <c r="N18" t="n">
-        <v>1749.7</v>
+        <v>31</v>
       </c>
       <c r="O18" t="n">
-        <v>32.2</v>
+        <v>89</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q18" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>213.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>74.09999999999999</v>
+        <v>27.95</v>
       </c>
       <c r="V18" t="n">
-        <v>76.8</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X18" t="n">
-        <v>26.55</v>
+        <v>26.8169675507093</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.218120805369127</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>27.6928953399542</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>27.2641439526698</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2705,24 +2548,15 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>136</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>174</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>500</v>
+        <v>577</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2730,82 +2564,82 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>71.47246748802191</v>
+        <v>85.0743345501559</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>25.5593291551416</v>
       </c>
       <c r="E19" t="n">
-        <v>24.1671624033313</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>903.7</v>
       </c>
       <c r="I19" t="n">
-        <v>587</v>
+        <v>809.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>747.3</v>
       </c>
       <c r="K19" t="n">
-        <v>168.7</v>
+        <v>2460.6</v>
       </c>
       <c r="L19" t="n">
-        <v>83</v>
+        <v>6.1</v>
       </c>
       <c r="M19" t="n">
-        <v>128.9</v>
+        <v>58.9</v>
       </c>
       <c r="N19" t="n">
-        <v>380.6</v>
+        <v>146.1</v>
       </c>
       <c r="O19" t="n">
-        <v>23.7</v>
+        <v>211.1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>36.3</v>
+        <v>63.5</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>8</v>
+        <v>24.7</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>24.7962821492233</v>
       </c>
       <c r="X19" t="n">
-        <v>25.15</v>
+        <v>24.4717629124263</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.277397260273973</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>25.3692386045327</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>24.7150115381059</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2817,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -2826,25 +2660,18 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>93</v>
-      </c>
-      <c r="AN19" t="inlineStr"/>
+        <v>146</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2375</v>
+        <v>2220</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2852,88 +2679,88 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>85.331470485715</v>
+        <v>88.7674595659999</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>17.7999288002847</v>
       </c>
       <c r="E20" t="n">
-        <v>23.4567901234567</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>38.3</v>
+        <v>30.9</v>
       </c>
       <c r="I20" t="n">
-        <v>17300</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="K20" t="n">
-        <v>121.2</v>
+        <v>56.2</v>
       </c>
       <c r="L20" t="n">
-        <v>69.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>197.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>388.1</v>
+        <v>7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>20.6582633053221</v>
       </c>
       <c r="X20" t="n">
-        <v>24.25</v>
+        <v>20.4418823263722</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.22992700729927</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>24.7326203208556</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>24.3805715703063</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2942,31 +2769,24 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>142</v>
-      </c>
-      <c r="AN20" t="inlineStr"/>
+        <v>164</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>488</v>
+        <v>754</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2974,123 +2794,114 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>82.8071981392755</v>
+        <v>65.49301657920751</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>31.2100121719047</v>
       </c>
       <c r="E21" t="n">
-        <v>45.3333333333333</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>50</v>
+        <v>283</v>
       </c>
       <c r="I21" t="n">
-        <v>1510</v>
+        <v>209</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="K21" t="n">
-        <v>249</v>
+        <v>776</v>
       </c>
       <c r="L21" t="n">
-        <v>279</v>
+        <v>27</v>
       </c>
       <c r="M21" t="n">
-        <v>352</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>880</v>
+        <v>46</v>
       </c>
       <c r="O21" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="P21" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>214</v>
+        <v>44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>23.4</v>
       </c>
       <c r="V21" t="n">
-        <v>60</v>
+        <v>0.28</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X21" t="n">
-        <v>22.15</v>
+        <v>22.8163986665956</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.24901185770751</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.2816399286988</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.789128418268</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>199</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>570</v>
+        <v>633</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3098,40 +2909,40 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>80.10493763784319</v>
+        <v>82.8868868355008</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>37.4213957794838</v>
       </c>
       <c r="E22" t="n">
-        <v>31.2213039485766</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="I22" t="n">
-        <v>1180</v>
+        <v>63.9</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>165.6</v>
       </c>
       <c r="K22" t="n">
-        <v>60</v>
+        <v>416.5</v>
       </c>
       <c r="L22" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3149,34 +2960,34 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>25.305576776165</v>
       </c>
       <c r="X22" t="n">
-        <v>27.2</v>
+        <v>24.856233988737</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.294670846394984</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>26.5066584133226</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3185,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -3197,22 +3008,15 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN22" t="inlineStr"/>
+        <v>236</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2308</v>
+        <v>1587</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3220,82 +3024,82 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>76.85541314928891</v>
+        <v>83.3414449768043</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>24.8970602317341</v>
       </c>
       <c r="E23" t="n">
-        <v>28.2828282828282</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>307.5</v>
       </c>
       <c r="I23" t="n">
-        <v>315</v>
+        <v>269.2</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>185.9</v>
       </c>
       <c r="K23" t="n">
-        <v>387.4</v>
+        <v>762.6</v>
       </c>
       <c r="L23" t="n">
-        <v>356.4</v>
+        <v>8.4</v>
       </c>
       <c r="M23" t="n">
-        <v>395.4</v>
+        <v>42.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1139.2</v>
+        <v>94.8</v>
       </c>
       <c r="O23" t="n">
-        <v>119.7</v>
+        <v>145.7</v>
       </c>
       <c r="P23" t="n">
-        <v>53.2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>175.5</v>
+        <v>18</v>
       </c>
       <c r="R23" t="n">
-        <v>348.4</v>
+        <v>78.8</v>
       </c>
       <c r="S23" t="n">
-        <v>14.9</v>
+        <v>96.8</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>127.4</v>
+        <v>23.15</v>
       </c>
       <c r="V23" t="n">
-        <v>142.3</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X23" t="n">
-        <v>23.05</v>
+        <v>23.0936433298824</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.298892988929889</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>22.8545963840081</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.1741916431478</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3319,24 +3123,15 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>256</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>349</v>
+        <v>706</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3344,77 +3139,79 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>87.6778480619566</v>
+        <v>78.3421933226861</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>23.3066800530675</v>
       </c>
       <c r="E24" t="n">
-        <v>23.9389897746315</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>36</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>287.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>232.1</v>
+      </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>196.2</v>
       </c>
       <c r="K24" t="n">
-        <v>125</v>
+        <v>715.5</v>
       </c>
       <c r="L24" t="n">
-        <v>231</v>
+        <v>15.7</v>
       </c>
       <c r="M24" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>591</v>
+        <v>38.2</v>
       </c>
       <c r="O24" t="n">
-        <v>15</v>
+        <v>53.90000000000001</v>
       </c>
       <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="Q24" t="n">
-        <v>16</v>
-      </c>
-      <c r="R24" t="n">
-        <v>39</v>
-      </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>26</v>
+        <v>20.95</v>
       </c>
       <c r="V24" t="n">
-        <v>26</v>
+        <v>0.21</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>21.5813598166539</v>
       </c>
       <c r="X24" t="n">
-        <v>27.85</v>
+        <v>21.1999238701354</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.332335329341317</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>28.7114845938375</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>27.1143398301643</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3435,26 +3232,21 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
+        <v>162</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3462,119 +3254,112 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>88.7510476081831</v>
+        <v>85.4307209673739</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>34.0866052266128</v>
       </c>
       <c r="E25" t="n">
-        <v>20.9366391184573</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>38</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>174</v>
+      </c>
+      <c r="I25" t="n">
+        <v>257</v>
+      </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="K25" t="n">
-        <v>217</v>
+        <v>566</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="M25" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>404</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="P25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>26.6424751718869</v>
       </c>
       <c r="X25" t="n">
-        <v>22</v>
+        <v>25.9240233435526</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.440794499618</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.7599008686688</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>146</v>
-      </c>
-      <c r="AN25" t="inlineStr"/>
+        <v>176</v>
+      </c>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>899</v>
+        <v>557</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3582,79 +3367,79 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>80.2974793076787</v>
+        <v>91.0891873906761</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>29.3575219240468</v>
       </c>
       <c r="E26" t="n">
-        <v>27.7769298861451</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>60</v>
+        <v>11.9</v>
       </c>
       <c r="I26" t="n">
-        <v>514</v>
+        <v>30.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>170.9</v>
       </c>
       <c r="K26" t="n">
-        <v>407</v>
+        <v>213.4</v>
       </c>
       <c r="L26" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>919</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>62</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>251</v>
+        <v>62.7</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>62.7</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>8</v>
+        <v>22.1</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>0.22</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>22.1224853577795</v>
       </c>
       <c r="X26" t="n">
-        <v>27.05</v>
+        <v>21.8532914302955</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.260450160771704</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>26.9117274486368</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3675,30 +3460,19 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>160</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="AK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>326</v>
+        <v>563</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3706,41 +3480,43 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>83.6231034362562</v>
+        <v>78.34722792607801</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>28.6726260752234</v>
       </c>
       <c r="E27" t="n">
-        <v>24.0238086700849</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>45</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="I27" t="n">
+        <v>278</v>
+      </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>531</v>
       </c>
       <c r="K27" t="n">
-        <v>196.4</v>
+        <v>1073</v>
       </c>
       <c r="L27" t="n">
-        <v>35.3</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>124.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>356.5</v>
+        <v>12</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -3755,34 +3531,34 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>23.35</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X27" t="n">
-        <v>22.9</v>
+        <v>23.4111342451446</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.303703703703704</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.6484228950307</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -3791,30 +3567,23 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>157</v>
-      </c>
-      <c r="AN27" t="inlineStr"/>
+        <v>210</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
